--- a/examples/excel/charts/charts-radar.xlsx
+++ b/examples/excel/charts/charts-radar.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1-Radar Fundamentals" sheetId="2" r:id="R9d70cd7ea3264c46"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2-Radar Styling" sheetId="3" r:id="Rb65761546eb2499e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3-Labels &amp; Legend" sheetId="4" r:id="Re006f568967049e7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4-Advanced" sheetId="5" r:id="Rcd3db22befa6475c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1-Radar Fundamentals" sheetId="2" r:id="R89673fc6fcf54b09"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2-Radar Styling" sheetId="3" r:id="R4af94d0f8af0402c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3-Labels &amp; Legend" sheetId="4" r:id="Rfa1e0eb5f210453f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4-Advanced" sheetId="5" r:id="R36ae83315581470a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -43,9 +43,11 @@
             <c:v>Alice</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="4472C4"/>
-            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="4472C4"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:cat>
             <c:strLit>
@@ -96,9 +98,11 @@
             <c:v>Bob</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="ED7D31"/>
-            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="ED7D31"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:cat>
             <c:strLit>
@@ -149,9 +153,11 @@
             <c:v>Carol</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="70AD47"/>
-            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="70AD47"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:cat>
             <c:strLit>
@@ -274,15 +280,29 @@
             <c:v>Alpha</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="4472C4"/>
-            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="4472C4"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:cat>
             <c:strLit>
-              <c:ptCount val="1"/>
-              <c:pt idx="0">
-                <c:v>Metric</c:v>
+              <c:ptCount val="5"/>
+              <c:pt idx="0">
+                <c:v>Metric A</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>Metric B</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>Metric C</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>Metric D</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>Metric E</c:v>
               </c:pt>
             </c:strLit>
           </c:cat>
@@ -315,15 +335,29 @@
             <c:v>Beta</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="ED7D31"/>
-            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="ED7D31"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:cat>
             <c:strLit>
-              <c:ptCount val="1"/>
-              <c:pt idx="0">
-                <c:v>Metric</c:v>
+              <c:ptCount val="5"/>
+              <c:pt idx="0">
+                <c:v>Metric A</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>Metric B</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>Metric C</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>Metric D</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>Metric E</c:v>
               </c:pt>
             </c:strLit>
           </c:cat>
@@ -356,15 +390,29 @@
             <c:v>Gamma</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="70AD47"/>
-            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="70AD47"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:cat>
             <c:strLit>
-              <c:ptCount val="1"/>
-              <c:pt idx="0">
-                <c:v>Metric</c:v>
+              <c:ptCount val="5"/>
+              <c:pt idx="0">
+                <c:v>Metric A</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>Metric B</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>Metric C</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>Metric D</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>Metric E</c:v>
               </c:pt>
             </c:strLit>
           </c:cat>
@@ -428,6 +476,7 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
+      <c:overlay val="1"/>
       <c:txPr>
         <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
         <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
@@ -443,7 +492,6 @@
           </a:pPr>
         </a:p>
       </c:txPr>
-      <c:overlay val="1"/>
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
@@ -494,11 +542,11 @@
             <c:v>Team</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="4472C4">
-                <a:alpha val="70000"/>
-              </a:srgbClr>
-            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="4472C4"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:cat>
             <c:strLit>
@@ -621,9 +669,11 @@
             <c:v>Dev</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="4472C4"/>
-            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="4472C4"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:cat>
             <c:strLit>
@@ -674,9 +724,11 @@
             <c:v>QA</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="ED7D31"/>
-            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="ED7D31"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:cat>
             <c:strLit>
@@ -727,9 +779,11 @@
             <c:v>Design</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="70AD47"/>
-            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="70AD47"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:cat>
             <c:strLit>
@@ -780,9 +834,11 @@
             <c:v>PM</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="FFC000"/>
-            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="FFC000"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:cat>
             <c:strLit>
@@ -833,9 +889,11 @@
             <c:v>DevOps</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="7030A0"/>
-            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:cat>
             <c:strLit>
@@ -991,9 +1049,11 @@
             <c:v>Score</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="2E75B6"/>
-            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="2E75B6"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:marker>
             <c:symbol val="diamond"/>
@@ -1125,11 +1185,11 @@
             <c:v>Candidate</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="4472C4">
-                <a:alpha val="65000"/>
-              </a:srgbClr>
-            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="4472C4"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:cat>
             <c:strLit>
@@ -1198,11 +1258,11 @@
             <c:v>Benchmark</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="BFBFBF">
-                <a:alpha val="65000"/>
-              </a:srgbClr>
-            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="BFBFBF"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:cat>
             <c:strLit>
@@ -1358,9 +1418,11 @@
             <c:v>Self</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="7030A0"/>
-            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:marker>
             <c:symbol val="square"/>
@@ -1533,11 +1595,6 @@
             <c:v>Before</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="C00000">
-                <a:alpha val="80000"/>
-              </a:srgbClr>
-            </a:solidFill>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
               <a:solidFill>
                 <a:srgbClr val="FFFFFF"/>
@@ -1593,11 +1650,6 @@
             <c:v>After</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="70AD47">
-                <a:alpha val="80000"/>
-              </a:srgbClr>
-            </a:solidFill>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
               <a:solidFill>
                 <a:srgbClr val="FFFFFF"/>
@@ -1652,7 +1704,7 @@
             <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
             <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:pPr>
-                <a:defRPr sz="900" b="0">
+                <a:defRPr sz="900">
                   <a:solidFill>
                     <a:srgbClr val="333333"/>
                   </a:solidFill>
@@ -1755,9 +1807,11 @@
             <c:v>Product A</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="2E75B6"/>
-            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="2E75B6"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:marker>
             <c:symbol val="circle"/>
@@ -1817,9 +1871,11 @@
             <c:v>Product B</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="C00000"/>
-            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="C00000"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:marker>
             <c:symbol val="circle"/>
@@ -1958,11 +2014,11 @@
             <c:v>Junior</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="4472C4">
-                <a:alpha val="60000"/>
-              </a:srgbClr>
-            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="4472C4"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:cat>
             <c:strLit>
@@ -2013,11 +2069,11 @@
             <c:v>Senior</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="70AD47">
-                <a:alpha val="60000"/>
-              </a:srgbClr>
-            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="70AD47"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:cat>
             <c:strLit>
@@ -2140,11 +2196,6 @@
             <c:v>Engineering</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="4472C4">
-                <a:alpha val="65000"/>
-              </a:srgbClr>
-            </a:solidFill>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="6350">
               <a:solidFill>
                 <a:srgbClr val="FFFFFF"/>
@@ -2200,11 +2251,6 @@
             <c:v>Marketing</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="ED7D31">
-                <a:alpha val="65000"/>
-              </a:srgbClr>
-            </a:solidFill>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="6350">
               <a:solidFill>
                 <a:srgbClr val="FFFFFF"/>
@@ -2260,11 +2306,6 @@
             <c:v>Sales</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="70AD47">
-                <a:alpha val="65000"/>
-              </a:srgbClr>
-            </a:solidFill>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="6350">
               <a:solidFill>
                 <a:srgbClr val="FFFFFF"/>
@@ -2405,9 +2446,11 @@
             <c:v>Team A</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="2E75B6"/>
-            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="2E75B6"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:cat>
             <c:strLit>
@@ -2530,11 +2573,11 @@
             <c:v>Region A</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="4472C4">
-                <a:alpha val="70000"/>
-              </a:srgbClr>
-            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="4472C4"/>
+              </a:solidFill>
+            </a:ln>
             <a:effectLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:outerShdw blurRad="50800" dist="25400" dir="18900000" algn="tl" rotWithShape="0">
                 <a:srgbClr val="000000">
@@ -2592,11 +2635,11 @@
             <c:v>Region B</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="ED7D31">
-                <a:alpha val="70000"/>
-              </a:srgbClr>
-            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="ED7D31"/>
+              </a:solidFill>
+            </a:ln>
             <a:effectLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:outerShdw blurRad="50800" dist="25400" dir="18900000" algn="tl" rotWithShape="0">
                 <a:srgbClr val="000000">
@@ -2726,15 +2769,29 @@
             <c:v>Actual</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="4472C4"/>
-            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="4472C4"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:cat>
             <c:strLit>
-              <c:ptCount val="1"/>
-              <c:pt idx="0">
-                <c:v>KPI</c:v>
+              <c:ptCount val="5"/>
+              <c:pt idx="0">
+                <c:v>KPI 1</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>KPI 2</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>KPI 3</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>KPI 4</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>KPI 5</c:v>
               </c:pt>
             </c:strLit>
           </c:cat>
@@ -2767,15 +2824,29 @@
             <c:v>Target</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="C00000"/>
-            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="C00000"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:cat>
             <c:strLit>
-              <c:ptCount val="1"/>
-              <c:pt idx="0">
-                <c:v>KPI</c:v>
+              <c:ptCount val="5"/>
+              <c:pt idx="0">
+                <c:v>KPI 1</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>KPI 2</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>KPI 3</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>KPI 4</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>KPI 5</c:v>
               </c:pt>
             </c:strLit>
           </c:cat>
@@ -2919,11 +2990,11 @@
             <c:v>Score</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="4472C4">
-                <a:alpha val="75000"/>
-              </a:srgbClr>
-            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="4472C4"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:cat>
             <c:strLit>
@@ -3066,9 +3137,11 @@
             <c:v>Performance</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="2E75B6"/>
-            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="2E75B6"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:marker>
             <c:symbol val="circle"/>
@@ -3213,7 +3286,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rc0f1822074d942ae"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rffdc8289f6f34392"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3243,7 +3316,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R006a3942619a44a3"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R21d3299037db4519"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3273,7 +3346,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R78ae732e5d894b5d"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rd6ec06625f9543c0"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3303,7 +3376,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R730e362f13264c9c"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R21257e5ebd9748c6"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3338,7 +3411,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R204fec3865ca4b93"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R95f728b9168148bc"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3368,7 +3441,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R5c5e4e5d3f9e433f"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R6c12f1e1b9864574"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3398,7 +3471,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R729f49cfa6ee4e50"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R295c254c80ed4840"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3428,7 +3501,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf2d7027c1c684315"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ra3c057c77d6a47b0"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3463,7 +3536,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R02acef6fec654578"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Re4db4a1572ff4a6c"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3493,7 +3566,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R25ddf61c49c74c79"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R765fdf3c10b04fab"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3523,7 +3596,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Re24ba691f9ec41c7"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R889edfa9eee3450d"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3553,7 +3626,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R1d12f8d9c21d4e66"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Re23534991d4d4572"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3588,7 +3661,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R28d0db8a94564497"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ra4a526cb966c4126"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3618,7 +3691,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rfc634588f2254c82"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Re8bd3f78c3a6423b"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3648,7 +3721,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rd0ac3853bf4a4c27"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R754ff39cccef4fbb"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3678,7 +3751,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R01db0f25544b4946"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R828a361862084c33"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3687,30 +3760,139 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="44546A"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E7E6E6"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4472C4"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="ED7D31"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A5A5A5"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="FFC000"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="5B9BD5"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="70AD47"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0563C1"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="954F72"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+        </a:ln>
+        <a:ln w="12700" cap="flat">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+        </a:ln>
+        <a:ln w="19050" cap="flat">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R60356eba98004ad7"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R11fc79e5d9254ad9"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R60d678299afb4e4f"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R90a9464cad564f8a"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5d9308d72f5649b4"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9ea5f86dd47c4ff9"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf170abb9e98a463d"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7fa3bf694f904637"/>
 </x:worksheet>
 </file>